--- a/data/trans_orig/IQ09_M-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en meses que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Tiempo medio en meses que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,17 +721,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,96</t>
+          <t>0,97; 4,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,95</t>
+          <t>1,2; 4,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,0</t>
+          <t>0,5; 2,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,59</t>
+          <t>1,12; 4,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,7</t>
+          <t>1,48; 3,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,46</t>
+          <t>1,84; 4,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,54</t>
+          <t>0,63; 3,54</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,97</t>
+          <t>0,42; 2,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,68</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,67</t>
+          <t>0,36; 1,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,82</t>
+          <t>0,93; 4,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,09</t>
+          <t>0,97; 3,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,49</t>
+          <t>0,4; 3,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,82</t>
+          <t>0,18; 1,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,49</t>
+          <t>0,95; 3,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,8</t>
+          <t>0,76; 2,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,57</t>
+          <t>0,61; 2,54</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,47</t>
+          <t>0,36; 5,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,58</t>
+          <t>0,4; 2,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,49</t>
+          <t>0,31; 4,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,74</t>
+          <t>0,53; 4,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,28</t>
+          <t>0,43; 3,29</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,2</t>
+          <t>0,07; 1,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,87</t>
+          <t>0,25; 3,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,18</t>
+          <t>0,69; 3,13</t>
         </is>
       </c>
     </row>
@@ -1141,57 +1141,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,62</t>
+          <t>0,0; 6,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,45</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 6,0</t>
+          <t>0,45; 5,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,41</t>
+          <t>0,71; 2,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,56</t>
+          <t>0,19; 2,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,69</t>
+          <t>0,58; 4,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,1</t>
+          <t>0,6; 2,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,76</t>
+          <t>0,08; 3,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,51</t>
+          <t>0,11; 1,5</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,0</t>
+          <t>0,28; 2,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,0</t>
+          <t>0,7; 2,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,79</t>
+          <t>0,75; 2,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,36</t>
+          <t>0,28; 1,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,37</t>
+          <t>0,51; 2,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,66</t>
+          <t>1,17; 2,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,95</t>
+          <t>0,96; 2,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,42</t>
+          <t>0,72; 2,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,89</t>
+          <t>0,58; 1,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,09</t>
+          <t>1,08; 2,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,39</t>
+          <t>1,08; 2,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,67</t>
+          <t>0,65; 1,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_M-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Edad-trans_orig.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,12</t>
+          <t>1,04; 4,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,83</t>
+          <t>1,36; 4,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -741,12 +741,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,58</t>
+          <t>1,08; 4,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,33</t>
+          <t>1,21; 5,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,74</t>
+          <t>1,39; 3,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,55</t>
+          <t>1,81; 4,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 4,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,7</t>
+          <t>0,42; 2,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,7</t>
+          <t>0,36; 1,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,78</t>
+          <t>0,93; 4,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,94</t>
+          <t>1,13; 3,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,22</t>
+          <t>0,43; 3,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,74</t>
+          <t>0,18; 1,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,29</t>
+          <t>0,93; 3,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,87</t>
+          <t>0,68; 2,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,54</t>
+          <t>0,57; 2,37</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,47 +1011,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,55</t>
+          <t>0,4; 2,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,46</t>
+          <t>0,51; 4,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,19</t>
+          <t>0,48; 4,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,29</t>
+          <t>0,42; 3,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,1</t>
+          <t>0,07; 1,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,2</t>
+          <t>0,25; 3,12</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,13</t>
+          <t>0,7; 3,13</t>
         </is>
       </c>
     </row>
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,0</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,93</t>
+          <t>0,0; 6,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,42 +1156,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,57</t>
+          <t>0,7; 6,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,52</t>
+          <t>0,64; 2,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 2,43</t>
+          <t>0,25; 2,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,62</t>
+          <t>0,82; 4,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,11</t>
+          <t>0,6; 2,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,58</t>
+          <t>0,07; 3,47</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,5</t>
+          <t>0,11; 1,54</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,16</t>
+          <t>0,23; 1,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,05</t>
+          <t>0,76; 2,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,86</t>
+          <t>0,74; 2,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,37</t>
+          <t>0,28; 1,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,28</t>
+          <t>0,5; 2,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,63</t>
+          <t>1,15; 2,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,73</t>
+          <t>1,06; 2,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,34</t>
+          <t>0,81; 2,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,97</t>
+          <t>0,59; 1,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,07</t>
+          <t>1,1; 2,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 2,43</t>
+          <t>1,09; 2,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,7</t>
+          <t>0,67; 1,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_M-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Edad-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -653,44 +653,44 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2,28</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4,0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>2,45</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,21</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1,54</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,28</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4,0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>2,36</t>
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,41</t>
+          <t>2,29</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,22</t>
+          <t>1,12; 4,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,93</t>
+          <t>1,08; 5,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,37 +741,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,55</t>
+          <t>0,91; 3,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,33</t>
+          <t>1,34; 4,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>0,56; 3,0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,64</t>
+          <t>1,41; 3,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,53</t>
+          <t>1,85; 4,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,54</t>
+          <t>0,85; 3,61</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,32</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,39</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>1,23</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,23</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,29</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,15</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,93</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -856,42 +856,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,09</t>
+          <t>0,0; 0,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,78</t>
+          <t>0,86; 4,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>1,19; 4,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,66</t>
+          <t>0,39; 3,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,77</t>
+          <t>0,47; 2,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,91</t>
+          <t>0,0; 0,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,25</t>
+          <t>0,48; 1,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,24</t>
+          <t>0,98; 3,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,93</t>
+          <t>0,67; 2,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,37</t>
+          <t>0,6; 2,51</t>
         </is>
       </c>
     </row>
@@ -928,44 +928,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,81</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,53</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,78</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,61</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0,61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,38</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,78</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>1,19</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1,38</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,41</t>
+          <t>1,42</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,31; 4,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,24</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,65</t>
+          <t>0,53; 4,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,7</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,36; 4,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,62</t>
+          <t>0,35; 2,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,37</t>
+          <t>0,49; 3,28</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,18</t>
+          <t>0,07; 1,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,12</t>
+          <t>0,19; 2,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,13</t>
+          <t>0,71; 3,17</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,58</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,36</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,74</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,58</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,19</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,55</t>
+          <t>0,74</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,87; 6,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,68; 2,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,72</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,42</t>
+          <t>0,25; 2,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,19</t>
+          <t>0,0; 6,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,39</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 7,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,51</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,35</t>
+          <t>0,57; 4,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,15</t>
+          <t>0,61; 2,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 3,47</t>
+          <t>0,07; 3,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,54</t>
+          <t>0,22; 1,76</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,74</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,8</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,35</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,84</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,27</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,52</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,19</t>
         </is>
       </c>
     </row>
@@ -1276,42 +1276,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,94</t>
+          <t>0,51; 2,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,04</t>
+          <t>1,15; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,8</t>
+          <t>1,11; 2,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,31</t>
+          <t>0,76; 2,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,28</t>
+          <t>0,28; 2,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,72</t>
+          <t>0,74; 2,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,87</t>
+          <t>0,73; 2,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,41</t>
+          <t>0,54; 1,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,25</t>
+          <t>1,1; 2,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,39</t>
+          <t>1,1; 2,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,69</t>
+          <t>0,8; 1,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_M-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_M-Edad-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en meses que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
+          <t>Tiempo medio en meses que los menores llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,255 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,28</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,45</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,21</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,54</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3,18</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.278863288054421</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.131393559028855</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>2.448570310713352</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>3.212139607244799</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>1.540452153101435</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>2.361331728771862</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>3.181289514553628</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>2.2934592105483</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 4,59</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,08; 5,33</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,91; 3,96</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,34; 4,95</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,56; 3,0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>1,41; 3,7</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1,85; 4,46</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,85; 3,61</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+      <c r="D5" s="5" t="n">
+        <v>1.119681381411498</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>1.077474091950049</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
+        <v>0.9091133628305523</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1.338724128418358</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>0.5620465880847336</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="n">
+        <v>1.412789899952278</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>1.847432699005168</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0.8502004685650302</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="n">
+        <v>4.591934497529435</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.325650948762437</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="n">
+        <v>3.964612014691228</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>4.953682932667662</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="5" t="inlineStr"/>
+      <c r="L6" s="5" t="n">
+        <v>3.699422519835766</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>4.457762828063808</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>3.607317311108575</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,23</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1,08</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1,59</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,87</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,86; 4,82</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,19; 4,09</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,39; 3,35</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,63</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,47; 2,97</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,68</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,48; 1,95</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0,18; 1,82</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0,98; 3,49</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>0,67; 2,8</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,6; 2,51</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.2988312455798357</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>2.319459289728432</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>2.394714066645857</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.230036129668781</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>1.234976489088228</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1.291530572152958</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0.1467845779207364</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>1.084456872474075</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>0.6431350145847522</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>1.827662649376941</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>1.588533660928488</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>1.172208404870613</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,53</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,61</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1,25</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.8618021528130548</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>1.18551653982705</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.3884532180924042</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.4749666051940241</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0.4818969370535701</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0.1820347986071296</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0.979737658420662</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0.6668094851477401</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0.5983125559722946</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,31; 4,49</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,41</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,19</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,53; 4,72</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,58</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,74</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,36; 4,47</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,35; 2,61</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0,49; 3,28</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 1,2</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>0,19; 2,87</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,71; 3,17</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.8740349002260021</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.821039326720485</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.08938497037165</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.351447365676932</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>3.625855168359669</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>2.974037902363243</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0.6758806631252362</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>1.945225646886716</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>1.815159604954832</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>3.487246204932089</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>2.795875343955249</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>2.505279964190183</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,277 +907,405 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,58</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,36</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,3</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,99</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2,21</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.812056015250745</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5293230716231293</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.7760203180363904</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.605560173742988</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.6123252998691489</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.3783560852419032</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1.77765914127417</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>1.194779631242771</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>1.382783715030169</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0.4351422956147338</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>1.247981507746232</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>1.419827869451697</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>0,87; 6,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,68; 2,41</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,82</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,25; 2,58</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,04</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,62</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,67</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0,57; 4,69</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0,61; 2,1</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 3,76</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,22; 1,76</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.3111249818495955</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.5301851652187413</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0.3601544036199638</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>0.3460332319218647</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>0.4888348727525493</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>0.06610354248689994</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0.1902971107556604</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0.7136977441149681</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.486638196385654</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.406996525467938</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.190888202927976</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.719090198842269</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.583725415367452</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>1.740691153672234</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>4.470456143574705</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>2.611817345901724</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>3.284884313781458</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>1.19677412819847</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>2.872299015032697</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>3.168679116327024</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2.58266113454353</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.362788130693867</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.2983995689563775</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.9876275136675582</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>1.530175021655489</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.7424918201021272</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1.401614399883019</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>0.1892742296871107</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>2.214710006176636</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>1.182346063247119</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0.8594454502078951</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>0.7367931254232289</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8706700566404448</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.6821568937671389</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.250205793416594</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0.5742366267396688</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>0.605826724667706</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0.0742422008469585</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>0.2166446293895064</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.996695548332053</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.413896715028838</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.8166324376088451</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.575524170576314</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>3.038090362011321</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>7.616246056306505</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>0.6734740046138175</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>4.692113304819664</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>2.104159474952472</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>3.757510538250183</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>1.759064747533272</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1,74</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,8</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,84</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,51; 2,37</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1,15; 2,66</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,11; 2,95</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,76; 2,43</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,28; 2,0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,74; 2,0</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,73; 2,79</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0,54; 1,61</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0,59; 1,89</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1,1; 2,09</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1,1; 2,39</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,8; 1,79</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>1.167296433376911</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1.740065232741119</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.797711188963817</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.353373606541376</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.8409027343496931</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.266231700892254</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>1.52049336977896</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0.9538646105745465</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>1.045449007429395</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>1.528415837243488</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>1.670083644795906</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>1.190212298740964</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.5129839542099085</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1.153774129576893</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>1.107789005976223</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.7629031590558345</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.2775037270853154</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.7441950134945083</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.7288295946140068</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.5423756588500399</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0.587063887217144</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>1.097662253162223</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>1.09607276225612</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>0.7969359973545388</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.367807184986848</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.664175506895318</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.947229504222053</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.430300423455491</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>2.003335847039142</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2.000566663112875</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>2.787070895355545</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>1.607979472326294</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>1.890215384103898</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>2.086061910788167</v>
+      </c>
+      <c r="M18" s="5" t="n">
+        <v>2.389178314634862</v>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>1.794806100107733</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1344,15 +1313,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
